--- a/databases/tabela_resumo_clusters_sus_inicio_kmeans3.xlsx
+++ b/databases/tabela_resumo_clusters_sus_inicio_kmeans3.xlsx
@@ -414,7 +414,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1: lowest unsafe abortion rates</t>
+          <t>1: lowest induced abortion rates</t>
         </is>
       </c>
       <c r="C2">
@@ -450,7 +450,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2: intermediary unsafe abortion rates</t>
+          <t>2: intermediary induced abortion rates</t>
         </is>
       </c>
       <c r="C3">
@@ -486,7 +486,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3: highest unsafe abortion rates</t>
+          <t>3: highest induced abortion rates</t>
         </is>
       </c>
       <c r="C4">
